--- a/output/evidence/第10期計画_エビデンス_0_索引.xlsx
+++ b/output/evidence/第10期計画_エビデンス_0_索引.xlsx
@@ -531,7 +531,7 @@
   <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
@@ -560,7 +560,11 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="4" t="inlineStr"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>収録ZIP</t>
+        </is>
+      </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
           <t>ファイル</t>
@@ -585,7 +589,8 @@
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>エビデンス_1
+データ集</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -610,7 +615,8 @@
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>エビデンス_1
+データ集</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -635,7 +641,8 @@
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>エビデンス_1
+データ集</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -660,12 +667,13 @@
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>エビデンス_2
+図表の画像</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>第10期計画_エビデンス_4_図表の画像.zip</t>
+          <t>（ZIPそのもの）</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -872,12 +880,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>④健康とくらしの調査の個票</t>
+          <t>④健康とくらしの調査の個票（4,729票）</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>当方に提供されていない。集計された指標値（20指標の年齢階級別・町別）を用いている。</t>
+          <t>個人情報のため。令和8年8月に受領し、クロス集計・分析（成果品「調査クロス集計・分析」24シート）に用いているが、本集及び成果品には集計値のみを収める。個票は受託者の作業環境にのみ保持し、リポジトリ及び納品データには格納していない。</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
@@ -909,10 +917,10 @@
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
     </row>
-    <row r="25" ht="39" customHeight="1">
+    <row r="25" ht="52" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>注1）本集は成果品ではない。仕様書４（10）が求める「分析資料・推計資料・図表・グラフ・クロス集計表の電子データ」の一部として位置づけられるものである。注2）図表の画像（PNG・79点）は「エビデンス_4_図表の画像」に収めている。注3）本集の各表は、生成スクリプトから機械的に書き出している。手作業による転記を経ていないため、成果品の数値との食い違いは生じない。</t>
+          <t>注1）本集は成果品ではない。仕様書４（10）が求める「分析資料・推計資料・図表・グラフ・クロス集計表の電子データ」の一部として位置づけられるものである。注2）図表の画像（PNG・79点）は「エビデンス_4_図表の画像」に収めている。注3）本集の各表は、成果品と同じデータモジュールから機械的に書き出している。したがって本集に収めた表と成果品の該当箇所との間に転記の誤りは生じない。ただしこれは「本集に収めた範囲」についての保証であり、成果品のすべての数値を保証するものではない。本集に収めていない数値（④健康とくらしの調査の集計値、見える化δ、事業所調査の照会中の項目など）は、各成果品の出典欄により確認いただきたい。</t>
         </is>
       </c>
     </row>

--- a/output/evidence/第10期計画_エビデンス_0_索引.xlsx
+++ b/output/evidence/第10期計画_エビデンス_0_索引.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>上記①〜⑫の各出典による</t>
+          <t>上記①〜⑮の各出典による</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>成果物の各表には出典を明記している。出典の表記は本集00シートの出典一覧の①〜⑫に対応する。</t>
+          <t>成果物の各表には出典を明記している。出典の表記は本集00シートの出典一覧の①〜⑮に対応する。</t>
         </is>
       </c>
       <c r="D15" s="8" t="n"/>
